--- a/hardware/expansion-board-v3/BOM_采购清单.xlsx
+++ b/hardware/expansion-board-v3/BOM_采购清单.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1664,37 +1664,37 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>二极管</t>
+          <t>电感</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ESD 3.3V/0.6pF</t>
+          <t>6.8uH</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0402</t>
+          <t>0805</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>TECH PUBLIC TPESD8L3.3CT5G</t>
+          <t>TDK MLZ2012N6R8LT000</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>C2830293</t>
+          <t>C82157</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>低结电容 ESD 管（≤0.6pF）</t>
+          <t>DCR&lt;300mΩ 且 Isat≥100mA</t>
         </is>
       </c>
     </row>
@@ -1706,60 +1706,64 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>B5819W</t>
+          <t>ESD 3.3V/0.6pF</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SOD-123</t>
+          <t>0402</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>JSMSEMI 1N5819W</t>
+          <t>TECH PUBLIC TPESD8L3.3CT5G</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>C963381</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr"/>
+          <t>C2830293</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>低结电容 ESD 管（≤0.6pF）</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>保险丝</t>
+          <t>二极管</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>6V/200mA</t>
+          <t>B5819W</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0805</t>
+          <t>SOD-123</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>金瑞 JK-SMD0805-020-30V</t>
+          <t>JSMSEMI 1N5819W</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>C516070</t>
+          <t>C963381</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr"/>
@@ -1767,17 +1771,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>三极管/MOS</t>
+          <t>保险丝</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AO3401A</t>
+          <t>6V/200mA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SOT-23</t>
+          <t>0805</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -1787,12 +1791,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>UMW AO3401A</t>
+          <t>金瑞 JK-SMD0805-020-30V</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>C347476</t>
+          <t>C516070</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr"/>
@@ -1800,35 +1804,68 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>三极管/MOS</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>XA17-G4K</t>
+          <t>AO3401A</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SOT-363/SC-70-6</t>
+          <t>SOT-23</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="n">
+        <v>6</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>UMW AO3401A</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>C347476</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>IC</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>XA17-G4K</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SOT-363/SC-70-6</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="n">
         <v>4</v>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>信路达 XA17-G4K</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>C513494</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/hardware/expansion-board-v3/BOM_采购清单.xlsx
+++ b/hardware/expansion-board-v3/BOM_采购清单.xlsx
@@ -1272,7 +1272,11 @@
           <t>0603</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>不限</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="n">
         <v>50</v>
@@ -1677,7 +1681,11 @@
           <t>0805</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>不限</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="n">
         <v>50</v>
